--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Март 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Март 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92555713441</v>
+        <v>46157.93113635006</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Март 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Март 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93113635006</v>
+        <v>46157.93137121811</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Март 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Март 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93137121811</v>
+        <v>46157.9338456604</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Март 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Март 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9338456604</v>
+        <v>46157.93696320999</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Март 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Март 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93696320999</v>
+        <v>46158.28205226875</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Март 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Март 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28205226875</v>
+        <v>46158.29653153942</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Март 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Март 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29653153942</v>
+        <v>46158.29808157471</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Март 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Март 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29808157471</v>
+        <v>46158.3337091122</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Март 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Март 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3337091122</v>
+        <v>46158.37222138204</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Март 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Март 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37222138204</v>
+        <v>46158.37275897652</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
